--- a/Ayushpathi_Test_Cases.xlsx
+++ b/Ayushpathi_Test_Cases.xlsx
@@ -19,6 +19,7 @@
     <sheet name="My Doctors — Scenarios" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="Receptionist Booking — S15" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Admin Appointments — S15" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="WhatsApp OTP — S15" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="1022">
   <si>
     <t xml:space="preserve">Ayushpathi — Pending Actions (updated Session 11)</t>
   </si>
@@ -334,6 +335,66 @@
   </si>
   <si>
     <t xml:space="preserve">New /hospital-admin/appointments page built Session 15. See Admin Appointments — S15 sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSG91 account setup + register 919361287432 as WhatsApp Business number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">External Setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required before OTP login works. See checklist in supabase/migrations/20260627_otp_phone_auth.sql</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create + submit 9 Meta OTP templates for approval (EN/HI/TA/TE/KN/ML/BN/GU/MR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSG91 / Meta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template body: "Your Ayushpathi verification code is {{1}}. Valid for 10 minutes." — submit per language in MSG91 portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set MSG91_AUTH_KEY + 9 template ID secrets in Supabase + deploy send-otp-whatsapp function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supabase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commands: supabase functions deploy send-otp-whatsapp --no-verify-jwt + supabase secrets set ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable Phone Auth in Supabase dashboard + register Send SMS hook → send-otp-whatsapp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboard: Authentication → Providers → Phone (enable). Authentication → Hooks → Send SMS Hook → Edge Function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test OTP-01 to OTP-13 on mobile after activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See WhatsApp OTP — S15 sheet</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -2351,6 +2412,12 @@
     <t xml:space="preserve">Returns hospital-scoped doctor roster for booking</t>
   </si>
   <si>
+    <t xml:space="preserve">WhatsApp OTP tests (OTP-01..13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New sheet: WhatsApp OTP — S15</t>
+  </si>
+  <si>
     <t xml:space="preserve">My Doctors Screen — Patient Consent Scenarios (Seed 003 + 004)</t>
   </si>
   <si>
@@ -2986,6 +3053,251 @@
   </si>
   <si>
     <t xml:space="preserve">Navigates to /hospital-admin/appointments (not /appointments/today). Shows hospital-scoped list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient Login — Phone Entry Screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default login screen shows phone+OTP mode (not email)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Expo app
+2. Observe login screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone number field + "Get OTP on WhatsApp" button shown by default. Language picker visible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff mode visible as link at bottom: "Staff login (email &amp; password)"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Language Picker — Changes OTP Button Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selecting Tamil changes button text to Tamil script</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. On login screen, change language to Tamil (தமிழ்)
+2. Observe button text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"WhatsApp-ல் OTP பெறுக" shown in Tamil. All labels change to Tamil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send OTP — Valid 10-digit Mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient enters valid 10-digit number and requests OTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter: 9876543210
+2. Tap "Get OTP on WhatsApp"
+3. Observe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loading spinner → OTP sent banner: "✅ OTP sent to +91 9876543210 via WhatsApp". OTP input appears. 60-second resend timer starts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires MSG91 + Supabase Phone Auth enabled. See migration checklist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send OTP — Invalid Number (&lt; 10 digits)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short number is rejected before API call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter: 98765
+2. Tap "Get OTP on WhatsApp"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: "Please enter a valid 10-digit mobile number." No API call made.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify OTP — Correct Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient enters correct 6-digit OTP and logs in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete OTP-03
+2. Enter correct 6-digit OTP from WhatsApp
+3. Tap "Verify &amp; Login"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session created. Routed to /(tabs)/ home screen. AsyncStorage lang key set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify OTP — Wrong Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect OTP shows friendly error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete OTP-03
+2. Enter wrong 6-digit OTP (e.g. 000000)
+3. Tap "Verify &amp; Login"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: "OTP expired or incorrect. Request a new one." Stays on OTP screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resend OTP — After Timer Expires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resend button activates after 60 seconds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete OTP-03
+2. Wait 60 seconds
+3. Tap "Resend OTP"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New OTP sent. Timer resets to 60. Previous OTP field cleared.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change Number — Before OTP Entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient can go back and change their phone number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete OTP-03
+2. Tap "Change number"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Returns to phone entry screen. Phone field cleared. OTP banner gone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Login Toggle — Doctor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff toggle shows email+password form for doctor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. On login screen, tap "Staff login (email &amp; password)"
+2. Enter doctor credentials
+3. Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email+password form shown. Login succeeds. Routed to /doctor-dashboard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctors/receptionists/admins use email+password — unchanged from before.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Login Toggle — Receptionist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receptionist uses staff mode (email+password)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tap "Staff login"
+2. Enter recep_h01@gmail.com / Ayush@2026!
+3. Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Routed to /(receptionist)/ home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edge Function — Per-Language OTP Message (Tamil)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamil patient receives OTP in Tamil script</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supabase Edge Function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kavitha.subramanian@demo.ayushpathi.in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Patient with ui_language=TA triggers OTP
+2. Check MSG91 delivery log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp message in Tamil: "உங்கள் Ayushpathi சரிபார்ப்பு குறியீடு *XXXXXX*..."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires patient record with ui_language=TA and mobile number linked to WA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edge Function — Email Fallback on WA Failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If MSG91 WA fails, OTP sent to patient email (if on record)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Temporarily set MSG91_AUTH_KEY to invalid value in secrets
+2. Trigger OTP
+3. Check patient email inbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edge function logs WA failure. Patient receives OTP via email from noreply@rasbros.com. Auth not blocked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires RESEND_API_KEY set in Supabase secrets + patient.email populated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edge Function — No Failure Propagation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auth is never blocked even if both WA and email fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set both MSG91_AUTH_KEY=invalid and no RESEND_API_KEY
+2. Trigger OTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edge function logs warnings. Returns {} (success) to Supabase. signInWithOtp() returns no error. App shows OTP screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP delivery fails silently — patient sees resend option after 60s</t>
   </si>
 </sst>
 </file>
@@ -3837,7 +4149,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -4388,7 +4700,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
         <v>85</v>
       </c>
@@ -4411,7 +4723,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
         <v>89</v>
       </c>
@@ -4434,7 +4746,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
         <v>92</v>
       </c>
@@ -4457,7 +4769,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
         <v>95</v>
       </c>
@@ -4480,7 +4792,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
         <v>98</v>
       </c>
@@ -4501,6 +4813,121 @@
       </c>
       <c r="G30" s="16" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -4525,45 +4952,45 @@
   <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="55" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="B1" s="55" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="D1" s="55" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="E1" s="55" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="F1" s="55" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="G1" s="55" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="I1" s="55" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="J1" s="55" t="s">
         <v>6</v>
@@ -4572,27 +4999,27 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>820</v>
+        <v>842</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>821</v>
+        <v>843</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>822</v>
+        <v>844</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>824</v>
+        <v>846</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>825</v>
+        <v>847</v>
       </c>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
@@ -4601,27 +5028,27 @@
       </c>
       <c r="K2" s="16"/>
     </row>
-    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>826</v>
+        <v>848</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>827</v>
+        <v>849</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>828</v>
+        <v>850</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>829</v>
+        <v>851</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>830</v>
+        <v>852</v>
       </c>
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
@@ -4630,27 +5057,27 @@
       </c>
       <c r="K3" s="17"/>
     </row>
-    <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>831</v>
+        <v>853</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>832</v>
+        <v>854</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>833</v>
+        <v>855</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>834</v>
+        <v>856</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>835</v>
+        <v>857</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
@@ -4659,27 +5086,27 @@
       </c>
       <c r="K4" s="16"/>
     </row>
-    <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>836</v>
+        <v>858</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>837</v>
+        <v>859</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>838</v>
+        <v>860</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>839</v>
+        <v>861</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>840</v>
+        <v>862</v>
       </c>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
@@ -4688,27 +5115,27 @@
       </c>
       <c r="K5" s="17"/>
     </row>
-    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>841</v>
+        <v>863</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>842</v>
+        <v>864</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>843</v>
+        <v>865</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>844</v>
+        <v>866</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>845</v>
+        <v>867</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
@@ -4716,30 +5143,30 @@
         <v>18</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>847</v>
+        <v>869</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>848</v>
+        <v>870</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>849</v>
+        <v>871</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>850</v>
+        <v>872</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>851</v>
+        <v>873</v>
       </c>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
@@ -4748,27 +5175,27 @@
       </c>
       <c r="K7" s="17"/>
     </row>
-    <row r="8" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>852</v>
+        <v>874</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>853</v>
+        <v>875</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>854</v>
+        <v>876</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>855</v>
+        <v>877</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>856</v>
+        <v>878</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
@@ -4777,27 +5204,27 @@
       </c>
       <c r="K8" s="16"/>
     </row>
-    <row r="9" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>857</v>
+        <v>879</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>858</v>
+        <v>880</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>859</v>
+        <v>881</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>860</v>
+        <v>882</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>861</v>
+        <v>883</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
@@ -4805,30 +5232,30 @@
         <v>18</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>863</v>
+        <v>885</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>864</v>
+        <v>886</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>865</v>
+        <v>887</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>866</v>
+        <v>888</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>867</v>
+        <v>889</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
@@ -4837,27 +5264,27 @@
       </c>
       <c r="K10" s="16"/>
     </row>
-    <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>868</v>
+        <v>890</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>869</v>
+        <v>891</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>870</v>
+        <v>892</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>871</v>
+        <v>893</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>872</v>
+        <v>894</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
@@ -4885,45 +5312,45 @@
   <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="55" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="B1" s="55" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="D1" s="55" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="E1" s="55" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="F1" s="55" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="G1" s="55" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="I1" s="55" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="J1" s="55" t="s">
         <v>6</v>
@@ -4932,27 +5359,27 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>873</v>
+        <v>895</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>874</v>
+        <v>896</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>875</v>
+        <v>897</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>876</v>
+        <v>898</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>877</v>
+        <v>899</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>878</v>
+        <v>900</v>
       </c>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
@@ -4961,27 +5388,27 @@
       </c>
       <c r="K2" s="16"/>
     </row>
-    <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>879</v>
+        <v>901</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>880</v>
+        <v>902</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>881</v>
+        <v>903</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>876</v>
+        <v>898</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>882</v>
+        <v>904</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>883</v>
+        <v>905</v>
       </c>
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
@@ -4990,27 +5417,27 @@
       </c>
       <c r="K3" s="17"/>
     </row>
-    <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>884</v>
+        <v>906</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>885</v>
+        <v>907</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>886</v>
+        <v>908</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>876</v>
+        <v>898</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>887</v>
+        <v>909</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>888</v>
+        <v>910</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
@@ -5018,30 +5445,30 @@
         <v>18</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>890</v>
+        <v>912</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>891</v>
+        <v>913</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>892</v>
+        <v>914</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>876</v>
+        <v>898</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>893</v>
+        <v>915</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
@@ -5050,27 +5477,27 @@
       </c>
       <c r="K5" s="17"/>
     </row>
-    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>876</v>
+        <v>898</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>899</v>
+        <v>921</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
@@ -5079,27 +5506,27 @@
       </c>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>900</v>
+        <v>922</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>901</v>
+        <v>923</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>902</v>
+        <v>924</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>876</v>
+        <v>898</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>903</v>
+        <v>925</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>904</v>
+        <v>926</v>
       </c>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
@@ -5108,27 +5535,27 @@
       </c>
       <c r="K7" s="17"/>
     </row>
-    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>905</v>
+        <v>927</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>906</v>
+        <v>928</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>907</v>
+        <v>929</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>876</v>
+        <v>898</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>908</v>
+        <v>930</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>909</v>
+        <v>931</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
@@ -5137,27 +5564,27 @@
       </c>
       <c r="K8" s="16"/>
     </row>
-    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>910</v>
+        <v>932</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>911</v>
+        <v>933</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>912</v>
+        <v>934</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>876</v>
+        <v>898</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>913</v>
+        <v>935</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>914</v>
+        <v>936</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
@@ -5166,27 +5593,27 @@
       </c>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>915</v>
+        <v>937</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>916</v>
+        <v>938</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>876</v>
+        <v>898</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>919</v>
+        <v>941</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
@@ -5195,27 +5622,27 @@
       </c>
       <c r="K10" s="16"/>
     </row>
-    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>920</v>
+        <v>942</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>921</v>
+        <v>943</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>922</v>
+        <v>944</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>923</v>
+        <v>945</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>924</v>
+        <v>946</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
@@ -5223,6 +5650,461 @@
         <v>18</v>
       </c>
       <c r="K11" s="17"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="36"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="55" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>947</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="F1" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="G1" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="H1" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="I1" s="55" t="s">
+        <v>215</v>
+      </c>
+      <c r="J1" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="55" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
+        <v>948</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>949</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>950</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>952</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
+        <v>955</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>956</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>958</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>959</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="17"/>
+    </row>
+    <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
+        <v>960</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>961</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>962</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>963</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>964</v>
+      </c>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
+        <v>966</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>967</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>968</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>969</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>970</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="17"/>
+    </row>
+    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>971</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>972</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>973</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>974</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>975</v>
+      </c>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
+        <v>976</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>977</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>978</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>979</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>980</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="17"/>
+    </row>
+    <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
+        <v>981</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>982</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>983</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>984</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>985</v>
+      </c>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>986</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>987</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>988</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>989</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>990</v>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>991</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>992</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>993</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>994</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>995</v>
+      </c>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="s">
+        <v>997</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>998</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>999</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="17"/>
+    </row>
+    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>1021</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5255,534 +6137,534 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="20" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="H10" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I10" s="22" t="s">
         <v>153</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="C14" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="G14" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="D14" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>149</v>
-      </c>
       <c r="H14" s="26" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H17" s="28" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I19" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -5792,7 +6674,7 @@
       <c r="G20" s="29"/>
       <c r="H20" s="29"/>
       <c r="I20" s="22" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -5831,37 +6713,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="L1" s="30" t="s">
         <v>7</v>
@@ -5869,552 +6751,552 @@
     </row>
     <row r="2" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="31" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="L3" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="K4" s="31" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="L4" s="31"/>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="D5" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>222</v>
       </c>
-      <c r="E5" s="33" t="s">
-        <v>202</v>
-      </c>
       <c r="F5" s="33" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="L5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="G6" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="J6" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="K6" s="31" t="s">
         <v>227</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>213</v>
-      </c>
-      <c r="J6" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="K6" s="31" t="s">
-        <v>207</v>
       </c>
       <c r="L6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="L7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="J8" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="B8" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="H8" s="31" t="s">
-        <v>236</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>213</v>
-      </c>
-      <c r="J8" s="35" t="s">
-        <v>214</v>
-      </c>
       <c r="K8" s="31" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="L8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C9" s="33" t="s">
         <v>237</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>217</v>
-      </c>
       <c r="D9" s="33" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="L9" s="33" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J10" s="35" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K10" s="31" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="L10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="L11" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J12" s="35" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="L12" s="31" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="H13" s="33" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="L13" s="33"/>
     </row>
     <row r="14" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K14" s="31" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="L14" s="31" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="H15" s="33" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="L15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="I16" s="35" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="J16" s="35" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K16" s="31" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="L16" s="31" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -6451,31 +7333,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="J1" s="30" t="s">
         <v>6</v>
@@ -6486,878 +7368,878 @@
     </row>
     <row r="2" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="31" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="H2" s="31"/>
       <c r="I2" s="36"/>
       <c r="J2" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="H3" s="33"/>
       <c r="I3" s="36"/>
       <c r="J3" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K3" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="H4" s="31"/>
       <c r="I4" s="36"/>
       <c r="J4" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K4" s="31"/>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="36"/>
       <c r="J5" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="B6" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>329</v>
+      </c>
+      <c r="D6" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="C6" s="31" t="s">
-        <v>309</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>288</v>
-      </c>
       <c r="E6" s="31" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="H6" s="31"/>
       <c r="I6" s="36"/>
       <c r="J6" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="H7" s="33"/>
       <c r="I7" s="36"/>
       <c r="J7" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="H8" s="31"/>
       <c r="I8" s="36"/>
       <c r="J8" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="36"/>
       <c r="J9" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="H10" s="31"/>
       <c r="I10" s="36"/>
       <c r="J10" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="H11" s="33"/>
       <c r="I11" s="36"/>
       <c r="J11" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K11" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="36"/>
       <c r="J12" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K12" s="31"/>
     </row>
     <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="H13" s="33"/>
       <c r="I13" s="36"/>
       <c r="J13" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K13" s="33"/>
     </row>
     <row r="14" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="H14" s="31"/>
       <c r="I14" s="36"/>
       <c r="J14" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K14" s="31" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H15" s="33"/>
       <c r="I15" s="36"/>
       <c r="J15" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="H16" s="31"/>
       <c r="I16" s="36"/>
       <c r="J16" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K16" s="31"/>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="H23" s="38"/>
       <c r="I23" s="38"/>
       <c r="J23" s="38" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="H24" s="38"/>
       <c r="I24" s="38"/>
       <c r="J24" s="38" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="38" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="H25" s="38"/>
       <c r="I25" s="38"/>
       <c r="J25" s="38" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="38" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="E26" s="38" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="G26" s="38" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="H26" s="38"/>
       <c r="I26" s="38"/>
       <c r="J26" s="38" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="H27" s="38"/>
       <c r="I27" s="38"/>
       <c r="J27" s="38" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="38" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="H28" s="38"/>
       <c r="I28" s="38"/>
       <c r="J28" s="38" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="38" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="H29" s="38"/>
       <c r="I29" s="38"/>
       <c r="J29" s="38" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="38" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="H30" s="38"/>
       <c r="I30" s="38"/>
       <c r="J30" s="38" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="38" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="H31" s="38"/>
       <c r="I31" s="38"/>
       <c r="J31" s="38" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -7404,31 +8286,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="J1" s="30" t="s">
         <v>6</v>
@@ -7439,660 +8321,660 @@
     </row>
     <row r="2" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="31" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="H2" s="31"/>
       <c r="I2" s="36"/>
       <c r="J2" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="H3" s="33"/>
       <c r="I3" s="36"/>
       <c r="J3" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K3" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="H4" s="31"/>
       <c r="I4" s="36"/>
       <c r="J4" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K4" s="31"/>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="36"/>
       <c r="J5" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="H6" s="31"/>
       <c r="I6" s="36"/>
       <c r="J6" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="H7" s="33"/>
       <c r="I7" s="36"/>
       <c r="J7" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="H8" s="31"/>
       <c r="I8" s="36"/>
       <c r="J8" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="36"/>
       <c r="J9" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="H10" s="31"/>
       <c r="I10" s="36"/>
       <c r="J10" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K10" s="31" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="H11" s="33"/>
       <c r="I11" s="36"/>
       <c r="J11" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K11" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="36"/>
       <c r="J12" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K12" s="31"/>
     </row>
     <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="H13" s="33"/>
       <c r="I13" s="36"/>
       <c r="J13" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="39" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
       <c r="J14" s="39" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="40" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F15" s="40" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="H15" s="40"/>
       <c r="I15" s="40"/>
       <c r="J15" s="40" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K15" s="40" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="39"/>
       <c r="J16" s="39" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="40" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="F17" s="40" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="H17" s="40"/>
       <c r="I17" s="40"/>
       <c r="J17" s="40" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K17" s="40"/>
     </row>
     <row r="18" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="39" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="39"/>
       <c r="J18" s="39" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K18" s="39" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="40" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F19" s="40" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="H19" s="40"/>
       <c r="I19" s="40"/>
       <c r="J19" s="40" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K19" s="40"/>
     </row>
     <row r="20" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="H20" s="39"/>
       <c r="I20" s="39"/>
       <c r="J20" s="39" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K20" s="39" t="s">
-        <v>554</v>
+        <v>574</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="40" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F21" s="40" t="s">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="G21" s="40" t="s">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="H21" s="40"/>
       <c r="I21" s="40"/>
       <c r="J21" s="40" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K21" s="40"/>
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="39" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>561</v>
+        <v>581</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="H22" s="39"/>
       <c r="I22" s="39"/>
       <c r="J22" s="39" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K22" s="39" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="40" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>569</v>
+        <v>589</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F23" s="40" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="G23" s="40" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="H23" s="40"/>
       <c r="I23" s="40"/>
       <c r="J23" s="40" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K23" s="40" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -8142,40 +9024,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>574</v>
+        <v>594</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="L1" s="30" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="M1" s="30" t="s">
         <v>6</v>
@@ -8186,394 +9068,394 @@
     </row>
     <row r="2" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="31" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="K2" s="31"/>
       <c r="L2" s="36"/>
       <c r="M2" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="N2" s="31" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="I3" s="33" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="36"/>
       <c r="M3" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="N3" s="33" t="s">
-        <v>593</v>
+        <v>613</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="D4" s="41" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>597</v>
+        <v>617</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="K4" s="31"/>
       <c r="L4" s="36"/>
       <c r="M4" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="N4" s="31"/>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>601</v>
+        <v>621</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="K5" s="33"/>
       <c r="L5" s="36"/>
       <c r="M5" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="N5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="K6" s="31"/>
       <c r="L6" s="36"/>
       <c r="M6" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
+        <v>630</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>631</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>632</v>
+      </c>
+      <c r="D7" s="34" t="s">
         <v>610</v>
       </c>
-      <c r="B7" s="33" t="s">
-        <v>611</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>612</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>590</v>
-      </c>
       <c r="E7" s="33" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="K7" s="33"/>
       <c r="L7" s="36"/>
       <c r="M7" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="N7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="K8" s="31"/>
       <c r="L8" s="36"/>
       <c r="M8" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="N8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>627</v>
+        <v>647</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>628</v>
+        <v>648</v>
       </c>
       <c r="K9" s="33"/>
       <c r="L9" s="36"/>
       <c r="M9" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="N9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="K10" s="31"/>
       <c r="L10" s="36"/>
       <c r="M10" s="35" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="N10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="I11" s="33" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="M11" s="34" t="s">
         <v>13</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -8618,297 +9500,297 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="31" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="F2" s="34" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="I2" s="34" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>661</v>
+        <v>681</v>
       </c>
       <c r="F3" s="42" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>663</v>
+        <v>683</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="K4" s="31" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>669</v>
+        <v>689</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>671</v>
+        <v>691</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>674</v>
+        <v>694</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>675</v>
+        <v>695</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>676</v>
+        <v>696</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D7" s="33" t="s">
+        <v>697</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>698</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>682</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>682</v>
+      </c>
+      <c r="I7" s="34" t="s">
         <v>677</v>
       </c>
-      <c r="E7" s="33" t="s">
-        <v>678</v>
-      </c>
-      <c r="F7" s="42" t="s">
-        <v>662</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>662</v>
-      </c>
-      <c r="I7" s="34" t="s">
-        <v>657</v>
-      </c>
       <c r="J7" s="33" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>679</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>681</v>
+        <v>701</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>683</v>
+        <v>703</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="43" t="s">
-        <v>684</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="s">
-        <v>685</v>
+        <v>705</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>686</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -8927,7 +9809,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -8937,10 +9819,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>687</v>
+        <v>707</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>688</v>
+        <v>708</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>7</v>
@@ -8948,26 +9830,26 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="46" t="s">
-        <v>689</v>
+        <v>709</v>
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="46"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="48" t="s">
-        <v>690</v>
+        <v>710</v>
       </c>
       <c r="B3" s="49" t="n">
         <f aca="false">COUNTA('API Tests — Session 6'!A2:A100)</f>
         <v>15</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>691</v>
+        <v>711</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="50" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="B4" s="51" t="n">
         <f aca="false">COUNTIF('API Tests — Session 6'!I2:I100,"Pass")</f>
@@ -8977,26 +9859,26 @@
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="48" t="s">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="B5" s="49" t="n">
         <f aca="false">COUNTIF('API Tests — Session 6'!I2:I100,"Fixed")</f>
         <v>4</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="50" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="B6" s="51" t="n">
         <f aca="false">COUNTIF('API Tests — Session 6'!I2:I100,"N/A")</f>
         <v>1</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9006,26 +9888,26 @@
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="46" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="B8" s="47"/>
       <c r="C8" s="46"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="48" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="B9" s="49" t="n">
         <f aca="false">COUNTA('Browser Tests'!A2:A100)</f>
         <v>30</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="50" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B10" s="51" t="n">
         <f aca="false">COUNTIF('Browser Tests'!J2:J100,"Not Started")</f>
@@ -9035,7 +9917,7 @@
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="B11" s="49" t="n">
         <f aca="false">COUNTIF('Browser Tests'!I2:I100,"Pass")</f>
@@ -9045,7 +9927,7 @@
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="50" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
       <c r="B12" s="51" t="n">
         <f aca="false">COUNTIF('Browser Tests'!I2:I100,"Fail")</f>
@@ -9060,26 +9942,26 @@
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="46" t="s">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="B14" s="47"/>
       <c r="C14" s="46"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="48" t="s">
-        <v>701</v>
+        <v>721</v>
       </c>
       <c r="B15" s="49" t="n">
         <f aca="false">COUNTA('Mobile Tests'!A2:A100)</f>
         <v>22</v>
       </c>
       <c r="C15" s="48" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="50" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B16" s="51" t="n">
         <f aca="false">COUNTIF('Mobile Tests'!J2:J100,"Not Started")</f>
@@ -9089,7 +9971,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="48" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="B17" s="49" t="n">
         <f aca="false">COUNTIF('Mobile Tests'!I2:I100,"Pass")</f>
@@ -9099,7 +9981,7 @@
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="50" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
       <c r="B18" s="51" t="n">
         <f aca="false">COUNTIF('Mobile Tests'!I2:I100,"Fail")</f>
@@ -9114,26 +9996,26 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="46" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
       <c r="B20" s="47"/>
       <c r="C20" s="46"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="48" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">COUNTA('Scenario Tests — Seed 003'!A2:A100)</f>
         <v>10</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="B22" s="51" t="n">
         <f aca="false">COUNTIF('Scenario Tests — Seed 003'!M2:M100,"Completed")+COUNTIF('Scenario Tests — Seed 003'!L2:L100,"Pass")</f>
@@ -9143,7 +10025,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="48" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">COUNTIF('Scenario Tests — Seed 003'!M2:M100,"Not Started")</f>
@@ -9158,14 +10040,14 @@
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="46" t="s">
-        <v>707</v>
+        <v>727</v>
       </c>
       <c r="B25" s="47"/>
       <c r="C25" s="46"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="50" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="B26" s="51" t="n">
         <f aca="false">COUNTA('API Tests — Session 6'!A2:A100)+COUNTA('Browser Tests'!A2:A100)+COUNTA('Mobile Tests'!A2:A100)+COUNTA('Scenario Tests — Seed 003'!A2:A100)</f>
@@ -9175,7 +10057,7 @@
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="48" t="s">
-        <v>709</v>
+        <v>729</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">COUNTIF('Browser Tests'!J2:J100,"Not Started")+COUNTIF('Mobile Tests'!J2:J100,"Not Started")+COUNTIF('Scenario Tests — Seed 003'!M2:M100,"Not Started")</f>
@@ -9185,93 +10067,104 @@
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="52" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="B28" s="52"/>
       <c r="C28" s="52"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="53" t="s">
-        <v>711</v>
+        <v>731</v>
       </c>
       <c r="B29" s="53" t="n">
         <v>10</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="53" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
       <c r="B30" s="53" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="53" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="B31" s="53" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>716</v>
+        <v>736</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="53" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
       <c r="B32" s="53" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="B34" s="16" t="n">
         <v>10</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>722</v>
+        <v>742</v>
       </c>
       <c r="B35" s="17" t="n">
         <v>10</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
-        <v>724</v>
+        <v>744</v>
       </c>
       <c r="B36" s="16" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>725</v>
+        <v>745</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>746</v>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>747</v>
       </c>
     </row>
   </sheetData>
@@ -9309,7 +10202,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="54" t="s">
-        <v>726</v>
+        <v>748</v>
       </c>
       <c r="B1" s="54"/>
       <c r="C1" s="54"/>
@@ -9327,43 +10220,43 @@
     </row>
     <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>574</v>
+        <v>594</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>727</v>
+        <v>749</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>728</v>
+        <v>750</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>729</v>
+        <v>751</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>730</v>
+        <v>752</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>731</v>
+        <v>753</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>732</v>
+        <v>754</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>733</v>
+        <v>755</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>734</v>
+        <v>756</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="N2" s="18" t="s">
         <v>6</v>
@@ -9371,422 +10264,422 @@
     </row>
     <row r="3" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="s">
-        <v>735</v>
+        <v>757</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>736</v>
+        <v>758</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>737</v>
+        <v>759</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>738</v>
+        <v>760</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>739</v>
+        <v>761</v>
       </c>
       <c r="G3" s="39" t="s">
-        <v>740</v>
+        <v>762</v>
       </c>
       <c r="H3" s="39" t="s">
-        <v>741</v>
+        <v>763</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>742</v>
+        <v>764</v>
       </c>
       <c r="J3" s="39" t="s">
-        <v>738</v>
+        <v>760</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>743</v>
+        <v>765</v>
       </c>
       <c r="L3" s="39" t="s">
-        <v>744</v>
+        <v>766</v>
       </c>
       <c r="M3" s="39"/>
       <c r="N3" s="39" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>745</v>
+        <v>767</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>746</v>
+        <v>768</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>747</v>
+        <v>769</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>749</v>
+        <v>771</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>750</v>
+        <v>772</v>
       </c>
       <c r="I4" s="40" t="s">
-        <v>751</v>
+        <v>773</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>753</v>
+        <v>775</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>754</v>
+        <v>776</v>
       </c>
       <c r="M4" s="40"/>
       <c r="N4" s="40" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
-        <v>755</v>
+        <v>777</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>756</v>
+        <v>778</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>757</v>
+        <v>779</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>749</v>
+        <v>771</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>750</v>
+        <v>772</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>758</v>
+        <v>780</v>
       </c>
       <c r="J5" s="39" t="s">
-        <v>759</v>
+        <v>781</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>753</v>
+        <v>775</v>
       </c>
       <c r="L5" s="39" t="s">
-        <v>760</v>
+        <v>782</v>
       </c>
       <c r="M5" s="39"/>
       <c r="N5" s="39" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>761</v>
+        <v>783</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>762</v>
+        <v>784</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>763</v>
+        <v>785</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="G6" s="40" t="s">
-        <v>764</v>
+        <v>786</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>765</v>
+        <v>787</v>
       </c>
       <c r="I6" s="40" t="s">
-        <v>766</v>
+        <v>788</v>
       </c>
       <c r="J6" s="40" t="s">
-        <v>767</v>
+        <v>789</v>
       </c>
       <c r="K6" s="40" t="s">
-        <v>768</v>
+        <v>790</v>
       </c>
       <c r="L6" s="40" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
       <c r="M6" s="40"/>
       <c r="N6" s="40" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
+        <v>792</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>793</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>794</v>
+      </c>
+      <c r="F7" s="39" t="s">
         <v>770</v>
       </c>
-      <c r="B7" s="39" t="s">
-        <v>771</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="39" t="s">
-        <v>772</v>
-      </c>
-      <c r="F7" s="39" t="s">
-        <v>748</v>
-      </c>
       <c r="G7" s="39" t="s">
-        <v>773</v>
+        <v>795</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>774</v>
+        <v>796</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>775</v>
+        <v>797</v>
       </c>
       <c r="J7" s="39" t="s">
-        <v>776</v>
+        <v>798</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>777</v>
+        <v>799</v>
       </c>
       <c r="L7" s="39" t="s">
-        <v>778</v>
+        <v>800</v>
       </c>
       <c r="M7" s="39"/>
       <c r="N7" s="39" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>779</v>
+        <v>801</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>780</v>
+        <v>802</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>781</v>
+        <v>803</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="G8" s="40" t="s">
-        <v>782</v>
+        <v>804</v>
       </c>
       <c r="H8" s="40" t="s">
-        <v>783</v>
+        <v>805</v>
       </c>
       <c r="I8" s="40" t="s">
-        <v>784</v>
+        <v>806</v>
       </c>
       <c r="J8" s="40" t="s">
-        <v>785</v>
+        <v>807</v>
       </c>
       <c r="K8" s="40" t="s">
-        <v>786</v>
+        <v>808</v>
       </c>
       <c r="L8" s="40" t="s">
-        <v>787</v>
+        <v>809</v>
       </c>
       <c r="M8" s="40"/>
       <c r="N8" s="40" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>788</v>
+        <v>810</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>789</v>
+        <v>811</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>790</v>
+        <v>812</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>791</v>
+        <v>813</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>792</v>
+        <v>814</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>793</v>
+        <v>815</v>
       </c>
       <c r="J9" s="39" t="s">
-        <v>794</v>
+        <v>816</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>795</v>
+        <v>817</v>
       </c>
       <c r="L9" s="39" t="s">
-        <v>796</v>
+        <v>818</v>
       </c>
       <c r="M9" s="39"/>
       <c r="N9" s="39" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>797</v>
+        <v>819</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E10" s="40" t="s">
-        <v>799</v>
+        <v>821</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>800</v>
+        <v>822</v>
       </c>
       <c r="H10" s="40" t="s">
-        <v>765</v>
+        <v>787</v>
       </c>
       <c r="I10" s="40" t="s">
-        <v>801</v>
+        <v>823</v>
       </c>
       <c r="J10" s="40" t="s">
-        <v>802</v>
+        <v>824</v>
       </c>
       <c r="K10" s="40" t="s">
-        <v>803</v>
+        <v>825</v>
       </c>
       <c r="L10" s="40" t="s">
-        <v>804</v>
+        <v>826</v>
       </c>
       <c r="M10" s="40"/>
       <c r="N10" s="40" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="39" t="s">
-        <v>805</v>
+        <v>827</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>806</v>
+        <v>828</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>807</v>
+        <v>829</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>808</v>
+        <v>830</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>809</v>
+        <v>831</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="J11" s="39" t="s">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>811</v>
+        <v>833</v>
       </c>
       <c r="L11" s="39" t="s">
-        <v>812</v>
+        <v>834</v>
       </c>
       <c r="M11" s="39"/>
       <c r="N11" s="39" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>813</v>
+        <v>835</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>814</v>
+        <v>836</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="G12" s="40" t="s">
-        <v>816</v>
+        <v>838</v>
       </c>
       <c r="H12" s="40" t="s">
-        <v>817</v>
+        <v>839</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="J12" s="40" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K12" s="40" t="s">
-        <v>818</v>
+        <v>840</v>
       </c>
       <c r="L12" s="40" t="s">
-        <v>819</v>
+        <v>841</v>
       </c>
       <c r="M12" s="40"/>
       <c r="N12" s="40" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/Ayushpathi_Test_Cases.xlsx
+++ b/Ayushpathi_Test_Cases.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Receptionist Booking — S15" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Admin Appointments — S15" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="WhatsApp OTP — S15" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Doctor Dashboard — S16" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="1022">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="1105">
   <si>
     <t xml:space="preserve">Ayushpathi — Pending Actions (updated Session 11)</t>
   </si>
@@ -395,6 +396,14 @@
   </si>
   <si>
     <t xml:space="preserve">See WhatsApp OTP — S15 sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run 005_doctor_rich_history.sql in Supabase SQL Editor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File: supabase/seeds/005_doctor_rich_history.sql
+Adds: 4 consent rows, 17 appointments, 8 consultations, 8 prescriptions for doctor_h01 + doctor_h02.
+Fixes "0 records" on all doctor dashboard buttons.</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -2418,6 +2427,33 @@
     <t xml:space="preserve">New sheet: WhatsApp OTP — S15</t>
   </si>
   <si>
+    <t xml:space="preserve">── SESSION 16 ──</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctor Dashboard tests (DD-01..12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New sheet: Doctor Dashboard — S16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seed 005 applied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">005_doctor_rich_history.sql — rich test data for doctor_h01 + doctor_h02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New consent rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ananya+Mohan → Dr. Priya; Ananya+Mohan → Dr. Arjun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New appointments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today/upcoming/completed/cancelled/no-show for both doctors</t>
+  </si>
+  <si>
     <t xml:space="preserve">My Doctors Screen — Patient Consent Scenarios (Seed 003 + 004)</t>
   </si>
   <si>
@@ -3298,6 +3334,237 @@
   </si>
   <si>
     <t xml:space="preserve">OTP delivery fails silently — patient sees resend option after 60s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctor Login — h02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login as doctor_h02@gmail.com and reach doctor dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/auth/login → /dashboard/doctor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open www.rasbros.com/auth/login
+2. Enter doctor_h02@gmail.com / Ayush@2026!
+3. Click Sign In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redirected to /dashboard/doctor. Welcome 'Dr. Priya Nair'. Dashboard cards visible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today's Queue — Dr. Priya Nair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctor sees all today's appointments across all statuses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/appointments/today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as doctor_h02
+2. Click 'Today's Appointments' or go to /appointments/today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sees ≥3 rows: Ravi Kumar ARRIVED, Ananya Krishnan IN_PROGRESS, Mohan Pillai CONFIRMED (teleconsult). Statuses shown as colour badges.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today's Queue — Dr. Arjun Sharma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctor sees all today's appointments including walk-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as doctor_h01
+2. Click 'Today's Appointments'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sees ≥4 rows: Ravi ARRIVED, Ananya BOOKED, Ravi walk-in BOOKED (REC tag), Mohan CONFIRMED.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upcoming Appointments — Dr. Priya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upcoming tab shows future bookings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/appointments/upcoming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as doctor_h02
+2. Go to /appointments/upcoming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shows ≥3 upcoming: Ravi +7d BOOKED, Ananya +4d BOOKED, Mohan +11d BOOKED. No past rows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Patients — Dr. Priya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active patients list reflects ACTIVE consent rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/patients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as doctor_h02
+2. Click 'Active Patients' or /patients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shows 3 patients: Ravi Kumar, Ananya Krishnan, Mohan Pillai. Count = 3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consent rows added by seed 005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Patients — Dr. Arjun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active patients: Ananya + Mohan shown; Ravi absent (REVOKED)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as doctor_h01
+2. Click 'Active Patients'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shows 2 patients: Ananya Krishnan, Mohan Pillai. Ravi Kumar NOT listed (consent REVOKED in seed 003).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consent for Ananya+Mohan added by seed 005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient History — Ananya under Dr. Priya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 past consultations visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/patients/[ananya_id]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as doctor_h02
+2. Open Ananya Krishnan → consultation history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 consultations: -46d (Homoeopathic intake), -29d (Arsenicum Album added), -15d (existing f1000000-08). Prescriptions expandable for each.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed 005 adds first two; f1000000-08 pre-existed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient History — Mohan under Dr. Priya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 past consultations visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/patients/[mohan_id]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as doctor_h02
+2. Open Mohan Pillai → consultation history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 consultations: -21d (Calc Fluor + Rhus Tox + Allium Sativum), -6d (Ledum Palustre added). Prescription medicines visible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient History — Ananya under Dr. Arjun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AYU consultations visible with Ayurvedic diagnoses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as doctor_h01
+2. Open Ananya Krishnan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 consultations: -41d (Vasa Avaleha intake — Tamaka Shwasa), -18d (Sitopaladi Churna follow-up). Diagnoses in Ayurveda nomenclature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prescription Detail — HOM medicines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prescription JSONB shows correct multi-medicine display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as doctor_h02
+2. Open Ananya → first consultation (-46d)
+3. Expand prescription</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shows: Natrum Muriaticum 30C (4 globules, once daily) + Calendula Q (topical). Entry: RECEPTIONIST. Verified by Dr. Priya ✓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELLED &amp; NO_SHOW status rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All terminal appointment statuses visible in history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/appointments/today or history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doctor_h02 / doctor_h01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as doctor_h02 — find Ravi Kumar -3d row
+2. Login as doctor_h01 — find Ananya -5d row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doctor_h02: Ravi Kumar -3d shows CANCELLED badge ('family emergency').
+doctor_h01: Ananya -5d shows NO_SHOW badge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboard Stat Cards match seed 005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stat cards show correct totals after seed is applied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as doctor_h02
+2. Observe Today / Upcoming / Active Patients cards on dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today: 3 | Upcoming: 3 | Active Patients: 3. All cards link correctly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f1000000-03 pre-existed; seed 005 adds 2 today + 2 upcoming</t>
   </si>
 </sst>
 </file>
@@ -3307,7 +3574,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3473,6 +3740,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -3480,7 +3755,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3607,6 +3882,12 @@
         <bgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor rgb="FF0066CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
@@ -3672,7 +3953,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="63">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3889,12 +4170,40 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="22" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3948,7 +4257,7 @@
       <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FFF2DCDB"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF2E75B6"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF92D050"/>
       <rgbColor rgb="FFFDECEA"/>
@@ -4149,7 +4458,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -4815,7 +5124,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
         <v>101</v>
       </c>
@@ -4838,7 +5147,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
         <v>106</v>
       </c>
@@ -4861,7 +5170,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
         <v>110</v>
       </c>
@@ -4884,7 +5193,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
         <v>114</v>
       </c>
@@ -4907,7 +5216,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
         <v>117</v>
       </c>
@@ -4928,6 +5237,29 @@
       </c>
       <c r="G35" s="17" t="s">
         <v>120</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -4965,61 +5297,61 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="55" t="s">
-        <v>299</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>300</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>210</v>
-      </c>
-      <c r="D1" s="55" t="s">
+      <c r="A1" s="57" t="s">
         <v>301</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="B1" s="57" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="F1" s="55" t="s">
-        <v>302</v>
-      </c>
-      <c r="G1" s="55" t="s">
+      <c r="D1" s="57" t="s">
         <v>303</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="E1" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="F1" s="57" t="s">
         <v>304</v>
       </c>
-      <c r="I1" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="J1" s="55" t="s">
+      <c r="G1" s="57" t="s">
+        <v>305</v>
+      </c>
+      <c r="H1" s="57" t="s">
+        <v>306</v>
+      </c>
+      <c r="I1" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="J1" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="55" t="s">
+      <c r="K1" s="57" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>843</v>
+        <v>854</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>847</v>
+        <v>858</v>
       </c>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
@@ -5030,25 +5362,25 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>849</v>
+        <v>860</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>850</v>
+        <v>861</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
@@ -5059,25 +5391,25 @@
     </row>
     <row r="4" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>853</v>
+        <v>864</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>854</v>
+        <v>865</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>855</v>
+        <v>866</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>856</v>
+        <v>867</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>857</v>
+        <v>868</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
@@ -5088,25 +5420,25 @@
     </row>
     <row r="5" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>858</v>
+        <v>869</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>859</v>
+        <v>870</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>860</v>
+        <v>871</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>861</v>
+        <v>872</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
@@ -5117,25 +5449,25 @@
     </row>
     <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>866</v>
+        <v>877</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>867</v>
+        <v>878</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
@@ -5143,30 +5475,30 @@
         <v>18</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>868</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>870</v>
+        <v>881</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>871</v>
+        <v>882</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>873</v>
+        <v>884</v>
       </c>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
@@ -5177,25 +5509,25 @@
     </row>
     <row r="8" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>875</v>
+        <v>886</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
@@ -5206,25 +5538,25 @@
     </row>
     <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>880</v>
+        <v>891</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>882</v>
+        <v>893</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
@@ -5232,30 +5564,30 @@
         <v>18</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>885</v>
+        <v>896</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>887</v>
+        <v>898</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>889</v>
+        <v>900</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
@@ -5266,25 +5598,25 @@
     </row>
     <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>890</v>
+        <v>901</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>891</v>
+        <v>902</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>893</v>
+        <v>904</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
@@ -5325,61 +5657,61 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="55" t="s">
-        <v>299</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>300</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>210</v>
-      </c>
-      <c r="D1" s="55" t="s">
+      <c r="A1" s="57" t="s">
         <v>301</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="B1" s="57" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="F1" s="55" t="s">
-        <v>302</v>
-      </c>
-      <c r="G1" s="55" t="s">
+      <c r="D1" s="57" t="s">
         <v>303</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="E1" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="F1" s="57" t="s">
         <v>304</v>
       </c>
-      <c r="I1" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="J1" s="55" t="s">
+      <c r="G1" s="57" t="s">
+        <v>305</v>
+      </c>
+      <c r="H1" s="57" t="s">
+        <v>306</v>
+      </c>
+      <c r="I1" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="J1" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="55" t="s">
+      <c r="K1" s="57" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
@@ -5390,25 +5722,25 @@
     </row>
     <row r="3" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
@@ -5419,25 +5751,25 @@
     </row>
     <row r="4" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
@@ -5445,30 +5777,30 @@
         <v>18</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>913</v>
+        <v>924</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>916</v>
+        <v>927</v>
       </c>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
@@ -5479,25 +5811,25 @@
     </row>
     <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>919</v>
+        <v>930</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
@@ -5508,25 +5840,25 @@
     </row>
     <row r="7" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>923</v>
+        <v>934</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>926</v>
+        <v>937</v>
       </c>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
@@ -5537,25 +5869,25 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>930</v>
+        <v>941</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
@@ -5566,25 +5898,25 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>932</v>
+        <v>943</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>933</v>
+        <v>944</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>934</v>
+        <v>945</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>935</v>
+        <v>946</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>936</v>
+        <v>947</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
@@ -5595,25 +5927,25 @@
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>937</v>
+        <v>948</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>938</v>
+        <v>949</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>939</v>
+        <v>950</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>940</v>
+        <v>951</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>941</v>
+        <v>952</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
@@ -5624,25 +5956,25 @@
     </row>
     <row r="11" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>942</v>
+        <v>953</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="D11" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>176</v>
-      </c>
       <c r="F11" s="17" t="s">
-        <v>945</v>
+        <v>956</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>946</v>
+        <v>957</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
@@ -5670,74 +6002,74 @@
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="55" t="s">
-        <v>299</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>300</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>210</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>947</v>
-      </c>
-      <c r="E1" s="55" t="s">
+      <c r="A1" s="57" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="57" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="F1" s="55" t="s">
-        <v>302</v>
-      </c>
-      <c r="G1" s="55" t="s">
-        <v>303</v>
-      </c>
-      <c r="H1" s="55" t="s">
+      <c r="D1" s="57" t="s">
+        <v>958</v>
+      </c>
+      <c r="E1" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="F1" s="57" t="s">
         <v>304</v>
       </c>
-      <c r="I1" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="J1" s="55" t="s">
+      <c r="G1" s="57" t="s">
+        <v>305</v>
+      </c>
+      <c r="H1" s="57" t="s">
+        <v>306</v>
+      </c>
+      <c r="I1" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="J1" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="55" t="s">
+      <c r="K1" s="57" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>948</v>
+        <v>959</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>952</v>
+        <v>963</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
@@ -5745,30 +6077,30 @@
         <v>18</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>955</v>
+        <v>966</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>957</v>
+        <v>968</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>958</v>
+        <v>969</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>959</v>
+        <v>970</v>
       </c>
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
@@ -5777,27 +6109,27 @@
       </c>
       <c r="K3" s="17"/>
     </row>
-    <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>960</v>
+        <v>971</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>961</v>
+        <v>972</v>
       </c>
       <c r="C4" s="16" t="s">
+        <v>973</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>962</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>951</v>
-      </c>
       <c r="E4" s="16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>963</v>
+        <v>974</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>964</v>
+        <v>975</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
@@ -5805,30 +6137,30 @@
         <v>18</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>966</v>
+        <v>977</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>967</v>
+        <v>978</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>969</v>
+        <v>980</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>970</v>
+        <v>981</v>
       </c>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
@@ -5837,27 +6169,27 @@
       </c>
       <c r="K5" s="17"/>
     </row>
-    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>973</v>
+        <v>984</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>974</v>
+        <v>985</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>975</v>
+        <v>986</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
@@ -5866,27 +6198,27 @@
       </c>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>976</v>
+        <v>987</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>980</v>
+        <v>991</v>
       </c>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
@@ -5895,27 +6227,27 @@
       </c>
       <c r="K7" s="17"/>
     </row>
-    <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>981</v>
+        <v>992</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>982</v>
+        <v>993</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>983</v>
+        <v>994</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>984</v>
+        <v>995</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>985</v>
+        <v>996</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
@@ -5924,27 +6256,27 @@
       </c>
       <c r="K8" s="16"/>
     </row>
-    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>986</v>
+        <v>997</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>987</v>
+        <v>998</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>988</v>
+        <v>999</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>989</v>
+        <v>1000</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>990</v>
+        <v>1001</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
@@ -5953,27 +6285,27 @@
       </c>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>991</v>
+        <v>1002</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>995</v>
+        <v>1006</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
@@ -5981,30 +6313,30 @@
         <v>18</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>997</v>
+        <v>1008</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
@@ -6013,27 +6345,27 @@
       </c>
       <c r="K11" s="17"/>
     </row>
-    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>1003</v>
+        <v>1014</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>1006</v>
+        <v>1017</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>1007</v>
+        <v>1018</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>1008</v>
+        <v>1019</v>
       </c>
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
@@ -6041,30 +6373,30 @@
         <v>18</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>1010</v>
+        <v>1021</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>1011</v>
+        <v>1022</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>1012</v>
+        <v>1023</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>1013</v>
+        <v>1024</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>1014</v>
+        <v>1025</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -6072,30 +6404,30 @@
         <v>18</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D14" s="16" t="s">
         <v>1016</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>1005</v>
-      </c>
       <c r="E14" s="16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>1020</v>
+        <v>1031</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="16"/>
@@ -6103,7 +6435,429 @@
         <v>18</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>1021</v>
+        <v>1032</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="57" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="57" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>303</v>
+      </c>
+      <c r="E1" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="F1" s="57" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1" s="57" t="s">
+        <v>305</v>
+      </c>
+      <c r="H1" s="57" t="s">
+        <v>306</v>
+      </c>
+      <c r="I1" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="J1" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="57" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="58" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G2" s="59" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H2" s="59"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="59"/>
+    </row>
+    <row r="3" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="61" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B3" s="62" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E3" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="62" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G3" s="62" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H3" s="62"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="62"/>
+    </row>
+    <row r="4" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="58" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E4" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G4" s="59" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H4" s="59"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="61" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C5" s="62" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D5" s="62" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E5" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="62" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G5" s="62" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H5" s="62"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="62"/>
+    </row>
+    <row r="6" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="58" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H6" s="59"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="59" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="61" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C7" s="62" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D7" s="62" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E7" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="62" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G7" s="62" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H7" s="62"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="62" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="58" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C8" s="59" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E8" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="59" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H8" s="59"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="59" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="61" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B9" s="62" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C9" s="62" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D9" s="62" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E9" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="62" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G9" s="62" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H9" s="62"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="62"/>
+    </row>
+    <row r="10" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="58" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C10" s="59" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E10" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="F10" s="59" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G10" s="59" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H10" s="59"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="59"/>
+    </row>
+    <row r="11" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="61" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B11" s="62" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C11" s="62" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D11" s="62" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E11" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11" s="62" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G11" s="62" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H11" s="62"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="62"/>
+    </row>
+    <row r="12" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="58" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B12" s="59" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C12" s="59" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D12" s="59" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E12" s="59" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F12" s="59" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G12" s="59" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H12" s="59"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="59"/>
+    </row>
+    <row r="13" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="61" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B13" s="62" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C13" s="62" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D13" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H13" s="62"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" s="62" t="s">
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -6137,534 +6891,534 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="20" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B6" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="I6" s="22" t="s">
         <v>155</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="I6" s="22" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B10" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>169</v>
-      </c>
       <c r="H10" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B12" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>178</v>
-      </c>
       <c r="G12" s="24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B14" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>186</v>
-      </c>
       <c r="F14" s="25" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B16" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F16" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="C16" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>195</v>
-      </c>
       <c r="G16" s="27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H17" s="28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I19" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -6674,7 +7428,7 @@
       <c r="G20" s="29"/>
       <c r="H20" s="29"/>
       <c r="I20" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -6713,37 +7467,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L1" s="30" t="s">
         <v>7</v>
@@ -6751,552 +7505,552 @@
     </row>
     <row r="2" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="31" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="J3" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="K3" s="33" t="s">
         <v>229</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>233</v>
-      </c>
-      <c r="J3" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="K3" s="33" t="s">
-        <v>227</v>
       </c>
       <c r="L3" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K4" s="31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L4" s="31"/>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B5" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="J5" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="C5" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>242</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="I5" s="34" t="s">
-        <v>233</v>
-      </c>
-      <c r="J5" s="35" t="s">
-        <v>234</v>
-      </c>
       <c r="K5" s="33" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B6" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="J6" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="C6" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="G6" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>233</v>
-      </c>
-      <c r="J6" s="35" t="s">
-        <v>234</v>
-      </c>
       <c r="K6" s="31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J8" s="35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L9" s="33" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="J10" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="K10" s="31" t="s">
         <v>264</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>268</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>233</v>
-      </c>
-      <c r="J10" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="K10" s="31" t="s">
-        <v>262</v>
       </c>
       <c r="L10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L11" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J12" s="35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L12" s="31" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H13" s="33" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L13" s="33"/>
     </row>
     <row r="14" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K14" s="31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L14" s="31" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H15" s="33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I16" s="35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J16" s="35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K16" s="31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L16" s="31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -7333,31 +8087,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J1" s="30" t="s">
         <v>6</v>
@@ -7368,878 +8122,878 @@
     </row>
     <row r="2" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="31" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H2" s="31"/>
       <c r="I2" s="36"/>
       <c r="J2" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H3" s="33"/>
       <c r="I3" s="36"/>
       <c r="J3" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K3" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H4" s="31"/>
       <c r="I4" s="36"/>
       <c r="J4" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K4" s="31"/>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="36"/>
       <c r="J5" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H6" s="31"/>
       <c r="I6" s="36"/>
       <c r="J6" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H7" s="33"/>
       <c r="I7" s="36"/>
       <c r="J7" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H8" s="31"/>
       <c r="I8" s="36"/>
       <c r="J8" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="36"/>
       <c r="J9" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H10" s="31"/>
       <c r="I10" s="36"/>
       <c r="J10" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H11" s="33"/>
       <c r="I11" s="36"/>
       <c r="J11" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K11" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="36"/>
       <c r="J12" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K12" s="31"/>
     </row>
     <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D13" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="E13" s="33" t="s">
-        <v>148</v>
-      </c>
       <c r="F13" s="33" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H13" s="33"/>
       <c r="I13" s="36"/>
       <c r="J13" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K13" s="33"/>
     </row>
     <row r="14" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H14" s="31"/>
       <c r="I14" s="36"/>
       <c r="J14" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K14" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H15" s="33"/>
       <c r="I15" s="36"/>
       <c r="J15" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H16" s="31"/>
       <c r="I16" s="36"/>
       <c r="J16" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K16" s="31"/>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H23" s="38"/>
       <c r="I23" s="38"/>
       <c r="J23" s="38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H24" s="38"/>
       <c r="I24" s="38"/>
       <c r="J24" s="38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="38" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H25" s="38"/>
       <c r="I25" s="38"/>
       <c r="J25" s="38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="38" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E26" s="38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G26" s="38" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H26" s="38"/>
       <c r="I26" s="38"/>
       <c r="J26" s="38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D27" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="E27" s="38" t="s">
-        <v>148</v>
-      </c>
       <c r="F27" s="38" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H27" s="38"/>
       <c r="I27" s="38"/>
       <c r="J27" s="38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="38" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H28" s="38"/>
       <c r="I28" s="38"/>
       <c r="J28" s="38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="38" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H29" s="38"/>
       <c r="I29" s="38"/>
       <c r="J29" s="38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="38" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H30" s="38"/>
       <c r="I30" s="38"/>
       <c r="J30" s="38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="38" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H31" s="38"/>
       <c r="I31" s="38"/>
       <c r="J31" s="38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -8286,31 +9040,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J1" s="30" t="s">
         <v>6</v>
@@ -8321,660 +9075,660 @@
     </row>
     <row r="2" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="31" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D2" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="E2" s="31" t="s">
-        <v>131</v>
-      </c>
       <c r="F2" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="H2" s="31"/>
       <c r="I2" s="36"/>
       <c r="J2" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H3" s="33"/>
       <c r="I3" s="36"/>
       <c r="J3" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K3" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H4" s="31"/>
       <c r="I4" s="36"/>
       <c r="J4" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K4" s="31"/>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="36"/>
       <c r="J5" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H6" s="31"/>
       <c r="I6" s="36"/>
       <c r="J6" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D7" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E7" s="33" t="s">
-        <v>131</v>
-      </c>
       <c r="F7" s="33" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H7" s="33"/>
       <c r="I7" s="36"/>
       <c r="J7" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H8" s="31"/>
       <c r="I8" s="36"/>
       <c r="J8" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D9" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E9" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="33" t="s">
-        <v>131</v>
-      </c>
       <c r="F9" s="33" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="36"/>
       <c r="J9" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H10" s="31"/>
       <c r="I10" s="36"/>
       <c r="J10" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K10" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H11" s="33"/>
       <c r="I11" s="36"/>
       <c r="J11" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K11" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="36"/>
       <c r="J12" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K12" s="31"/>
     </row>
     <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D13" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="33" t="s">
-        <v>131</v>
-      </c>
       <c r="F13" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H13" s="33"/>
       <c r="I13" s="36"/>
       <c r="J13" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="39" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
       <c r="J14" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="40" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F15" s="40" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H15" s="40"/>
       <c r="I15" s="40"/>
       <c r="J15" s="40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K15" s="40" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="39"/>
       <c r="J16" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="40" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F17" s="40" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H17" s="40"/>
       <c r="I17" s="40"/>
       <c r="J17" s="40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K17" s="40"/>
     </row>
     <row r="18" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="39" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="39"/>
       <c r="J18" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K18" s="39" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="40" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F19" s="40" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H19" s="40"/>
       <c r="I19" s="40"/>
       <c r="J19" s="40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K19" s="40"/>
     </row>
     <row r="20" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H20" s="39"/>
       <c r="I20" s="39"/>
       <c r="J20" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K20" s="39" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="40" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F21" s="40" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G21" s="40" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H21" s="40"/>
       <c r="I21" s="40"/>
       <c r="J21" s="40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K21" s="40"/>
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="39" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H22" s="39"/>
       <c r="I22" s="39"/>
       <c r="J22" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K22" s="39" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="40" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F23" s="40" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G23" s="40" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H23" s="40"/>
       <c r="I23" s="40"/>
       <c r="J23" s="40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K23" s="40" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -9024,40 +9778,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L1" s="30" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M1" s="30" t="s">
         <v>6</v>
@@ -9068,394 +9822,394 @@
     </row>
     <row r="2" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="31" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K2" s="31"/>
       <c r="L2" s="36"/>
       <c r="M2" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N2" s="31" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I3" s="33" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="36"/>
       <c r="M3" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N3" s="33" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D4" s="41" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="K4" s="31"/>
       <c r="L4" s="36"/>
       <c r="M4" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N4" s="31"/>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K5" s="33"/>
       <c r="L5" s="36"/>
       <c r="M5" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="K6" s="31"/>
       <c r="L6" s="36"/>
       <c r="M6" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="K7" s="33"/>
       <c r="L7" s="36"/>
       <c r="M7" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="K8" s="31"/>
       <c r="L8" s="36"/>
       <c r="M8" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="K9" s="33"/>
       <c r="L9" s="36"/>
       <c r="M9" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K10" s="31"/>
       <c r="L10" s="36"/>
       <c r="M10" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I11" s="33" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M11" s="34" t="s">
         <v>13</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -9500,297 +10254,297 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="31" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F2" s="34" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I2" s="34" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
+        <v>681</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>682</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>683</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>684</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>684</v>
+      </c>
+      <c r="I3" s="34" t="s">
         <v>679</v>
       </c>
-      <c r="B3" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>680</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>681</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>682</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>682</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>677</v>
-      </c>
       <c r="J3" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K4" s="31" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="43" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
   </sheetData>
@@ -9809,7 +10563,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -9819,10 +10573,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>7</v>
@@ -9830,26 +10584,26 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="46" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="46"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="48" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B3" s="49" t="n">
         <f aca="false">COUNTA('API Tests — Session 6'!A2:A100)</f>
         <v>15</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B4" s="51" t="n">
         <f aca="false">COUNTIF('API Tests — Session 6'!I2:I100,"Pass")</f>
@@ -9859,26 +10613,26 @@
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="48" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B5" s="49" t="n">
         <f aca="false">COUNTIF('API Tests — Session 6'!I2:I100,"Fixed")</f>
         <v>4</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="50" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B6" s="51" t="n">
         <f aca="false">COUNTIF('API Tests — Session 6'!I2:I100,"N/A")</f>
         <v>1</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9888,26 +10642,26 @@
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="46" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B8" s="47"/>
       <c r="C8" s="46"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="48" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B9" s="49" t="n">
         <f aca="false">COUNTA('Browser Tests'!A2:A100)</f>
         <v>30</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B10" s="51" t="n">
         <f aca="false">COUNTIF('Browser Tests'!J2:J100,"Not Started")</f>
@@ -9917,7 +10671,7 @@
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B11" s="49" t="n">
         <f aca="false">COUNTIF('Browser Tests'!I2:I100,"Pass")</f>
@@ -9927,7 +10681,7 @@
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="50" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B12" s="51" t="n">
         <f aca="false">COUNTIF('Browser Tests'!I2:I100,"Fail")</f>
@@ -9942,26 +10696,26 @@
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="46" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B14" s="47"/>
       <c r="C14" s="46"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="48" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B15" s="49" t="n">
         <f aca="false">COUNTA('Mobile Tests'!A2:A100)</f>
         <v>22</v>
       </c>
       <c r="C15" s="48" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B16" s="51" t="n">
         <f aca="false">COUNTIF('Mobile Tests'!J2:J100,"Not Started")</f>
@@ -9971,7 +10725,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="48" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B17" s="49" t="n">
         <f aca="false">COUNTIF('Mobile Tests'!I2:I100,"Pass")</f>
@@ -9981,7 +10735,7 @@
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="50" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B18" s="51" t="n">
         <f aca="false">COUNTIF('Mobile Tests'!I2:I100,"Fail")</f>
@@ -9996,26 +10750,26 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="46" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B20" s="47"/>
       <c r="C20" s="46"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="48" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">COUNTA('Scenario Tests — Seed 003'!A2:A100)</f>
         <v>10</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B22" s="51" t="n">
         <f aca="false">COUNTIF('Scenario Tests — Seed 003'!M2:M100,"Completed")+COUNTIF('Scenario Tests — Seed 003'!L2:L100,"Pass")</f>
@@ -10025,7 +10779,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">COUNTIF('Scenario Tests — Seed 003'!M2:M100,"Not Started")</f>
@@ -10040,14 +10794,14 @@
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="46" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B25" s="47"/>
       <c r="C25" s="46"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="50" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B26" s="51" t="n">
         <f aca="false">COUNTA('API Tests — Session 6'!A2:A100)+COUNTA('Browser Tests'!A2:A100)+COUNTA('Mobile Tests'!A2:A100)+COUNTA('Scenario Tests — Seed 003'!A2:A100)</f>
@@ -10057,7 +10811,7 @@
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="48" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">COUNTIF('Browser Tests'!J2:J100,"Not Started")+COUNTIF('Mobile Tests'!J2:J100,"Not Started")+COUNTIF('Scenario Tests — Seed 003'!M2:M100,"Not Started")</f>
@@ -10067,104 +10821,155 @@
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="52" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B28" s="52"/>
       <c r="C28" s="52"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="53" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B29" s="53" t="n">
         <v>10</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="53" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B30" s="53" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="53" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B31" s="53" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="53" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B32" s="53" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B34" s="16" t="n">
         <v>10</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B35" s="17" t="n">
         <v>10</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B36" s="16" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B37" s="17" t="n">
         <v>13</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>747</v>
+        <v>749</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="54" t="s">
+        <v>750</v>
+      </c>
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="55" t="s">
+        <v>751</v>
+      </c>
+      <c r="B40" s="55" t="n">
+        <v>12</v>
+      </c>
+      <c r="C40" s="55" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="55" t="s">
+        <v>753</v>
+      </c>
+      <c r="B41" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="55" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="55" t="s">
+        <v>755</v>
+      </c>
+      <c r="B42" s="55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="55" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="55" t="s">
+        <v>757</v>
+      </c>
+      <c r="B43" s="55" t="n">
+        <v>17</v>
+      </c>
+      <c r="C43" s="55" t="s">
+        <v>758</v>
       </c>
     </row>
   </sheetData>
@@ -10201,62 +11006,62 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="54" t="s">
-        <v>748</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
+      <c r="A1" s="56" t="s">
+        <v>759</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
     </row>
     <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N2" s="18" t="s">
         <v>6</v>
@@ -10264,422 +11069,422 @@
     </row>
     <row r="3" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="s">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>759</v>
+        <v>770</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>760</v>
+        <v>771</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>761</v>
+        <v>772</v>
       </c>
       <c r="G3" s="39" t="s">
-        <v>762</v>
+        <v>773</v>
       </c>
       <c r="H3" s="39" t="s">
-        <v>763</v>
+        <v>774</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>764</v>
+        <v>775</v>
       </c>
       <c r="J3" s="39" t="s">
-        <v>760</v>
+        <v>771</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>765</v>
+        <v>776</v>
       </c>
       <c r="L3" s="39" t="s">
-        <v>766</v>
+        <v>777</v>
       </c>
       <c r="M3" s="39"/>
       <c r="N3" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>767</v>
+        <v>778</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>768</v>
+        <v>779</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>771</v>
+        <v>782</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>772</v>
+        <v>783</v>
       </c>
       <c r="I4" s="40" t="s">
-        <v>773</v>
+        <v>784</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>774</v>
+        <v>785</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="M4" s="40"/>
       <c r="N4" s="40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
-        <v>777</v>
+        <v>788</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>779</v>
+        <v>790</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>771</v>
+        <v>782</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>772</v>
+        <v>783</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>780</v>
+        <v>791</v>
       </c>
       <c r="J5" s="39" t="s">
-        <v>781</v>
+        <v>792</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="L5" s="39" t="s">
-        <v>782</v>
+        <v>793</v>
       </c>
       <c r="M5" s="39"/>
       <c r="N5" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>783</v>
+        <v>794</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>785</v>
+        <v>796</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="G6" s="40" t="s">
-        <v>786</v>
+        <v>797</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="I6" s="40" t="s">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="J6" s="40" t="s">
-        <v>789</v>
+        <v>800</v>
       </c>
       <c r="K6" s="40" t="s">
-        <v>790</v>
+        <v>801</v>
       </c>
       <c r="L6" s="40" t="s">
-        <v>791</v>
+        <v>802</v>
       </c>
       <c r="M6" s="40"/>
       <c r="N6" s="40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
-        <v>792</v>
+        <v>803</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>793</v>
+        <v>804</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>794</v>
+        <v>805</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>795</v>
+        <v>806</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="J7" s="39" t="s">
-        <v>798</v>
+        <v>809</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>799</v>
+        <v>810</v>
       </c>
       <c r="L7" s="39" t="s">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="M7" s="39"/>
       <c r="N7" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>801</v>
+        <v>812</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>802</v>
+        <v>813</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>803</v>
+        <v>814</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="G8" s="40" t="s">
-        <v>804</v>
+        <v>815</v>
       </c>
       <c r="H8" s="40" t="s">
-        <v>805</v>
+        <v>816</v>
       </c>
       <c r="I8" s="40" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="J8" s="40" t="s">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="K8" s="40" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="L8" s="40" t="s">
-        <v>809</v>
+        <v>820</v>
       </c>
       <c r="M8" s="40"/>
       <c r="N8" s="40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>810</v>
+        <v>821</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>811</v>
+        <v>822</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>812</v>
+        <v>823</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>813</v>
+        <v>824</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>814</v>
+        <v>825</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="J9" s="39" t="s">
-        <v>816</v>
+        <v>827</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>817</v>
+        <v>828</v>
       </c>
       <c r="L9" s="39" t="s">
-        <v>818</v>
+        <v>829</v>
       </c>
       <c r="M9" s="39"/>
       <c r="N9" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>819</v>
+        <v>830</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>820</v>
+        <v>831</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E10" s="40" t="s">
-        <v>821</v>
+        <v>832</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>822</v>
+        <v>833</v>
       </c>
       <c r="H10" s="40" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="I10" s="40" t="s">
-        <v>823</v>
+        <v>834</v>
       </c>
       <c r="J10" s="40" t="s">
-        <v>824</v>
+        <v>835</v>
       </c>
       <c r="K10" s="40" t="s">
-        <v>825</v>
+        <v>836</v>
       </c>
       <c r="L10" s="40" t="s">
-        <v>826</v>
+        <v>837</v>
       </c>
       <c r="M10" s="40"/>
       <c r="N10" s="40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="39" t="s">
-        <v>827</v>
+        <v>838</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>829</v>
+        <v>840</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>830</v>
+        <v>841</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>831</v>
+        <v>842</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>832</v>
+        <v>843</v>
       </c>
       <c r="J11" s="39" t="s">
-        <v>832</v>
+        <v>843</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>833</v>
+        <v>844</v>
       </c>
       <c r="L11" s="39" t="s">
-        <v>834</v>
+        <v>845</v>
       </c>
       <c r="M11" s="39"/>
       <c r="N11" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>835</v>
+        <v>846</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>836</v>
+        <v>847</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>837</v>
+        <v>848</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="G12" s="40" t="s">
-        <v>838</v>
+        <v>849</v>
       </c>
       <c r="H12" s="40" t="s">
-        <v>839</v>
+        <v>850</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J12" s="40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K12" s="40" t="s">
-        <v>840</v>
+        <v>851</v>
       </c>
       <c r="L12" s="40" t="s">
-        <v>841</v>
+        <v>852</v>
       </c>
       <c r="M12" s="40"/>
       <c r="N12" s="40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
